--- a/artfynd/A 364-2026 artfynd.xlsx
+++ b/artfynd/A 364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AZ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6769926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13440231</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17300779</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17300780</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1306,6 +1331,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55768328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1432,6 +1462,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188637</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1558,6 +1593,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188639</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1684,6 +1724,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188640</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1810,6 +1855,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188641</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1936,6 +1986,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188643</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2062,6 +2117,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188644</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2188,6 +2248,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188645</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2314,6 +2379,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188646</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2440,6 +2510,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188647</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2566,6 +2641,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2692,6 +2772,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2818,6 +2903,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188651</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2944,6 +3034,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188652</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3070,6 +3165,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188653</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3196,6 +3296,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188696</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3322,6 +3427,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188697</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3462,6 +3572,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113373</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3602,6 +3717,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113374</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3742,6 +3862,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113375</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3882,6 +4007,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113376</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4022,6 +4152,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113377</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4162,6 +4297,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113378</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4302,6 +4442,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113379</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4442,6 +4587,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68113380</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4582,6 +4732,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882389</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4722,6 +4877,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882390</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4862,6 +5022,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882391</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5002,6 +5167,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882392</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5142,6 +5312,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882458</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5282,6 +5457,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882459</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5422,6 +5602,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882460</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5562,6 +5747,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882461</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5702,6 +5892,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882462</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5842,6 +6037,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882463</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5982,6 +6182,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882464</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6122,6 +6327,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882465</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6262,6 +6472,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882466</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6402,6 +6617,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882467</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6542,6 +6762,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882468</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6682,6 +6907,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882470</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6822,6 +7052,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882471</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6962,6 +7197,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882513</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7102,6 +7342,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882514</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7242,6 +7487,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882515</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7377,6 +7627,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758636</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7512,6 +7767,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758637</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7647,6 +7907,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758638</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7782,6 +8047,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758639</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7917,6 +8187,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758641</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8052,6 +8327,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758642</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8187,6 +8467,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758643</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8317,6 +8602,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116754</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8447,6 +8737,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116756</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8577,6 +8872,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116759</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8707,6 +9007,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116760</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8837,6 +9142,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116761</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8967,6 +9277,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116762</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9097,6 +9412,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116763</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9227,6 +9547,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116764</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9357,6 +9682,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116765</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9487,6 +9817,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116767</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9617,6 +9952,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116768</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9747,6 +10087,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116769</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9877,6 +10222,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116770</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10007,6 +10357,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116771</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10137,6 +10492,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116772</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10267,6 +10627,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116773</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10397,6 +10762,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116774</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10527,6 +10897,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116775</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10657,6 +11032,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116778</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10787,6 +11167,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116779</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10917,6 +11302,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116780</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11047,6 +11437,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116781</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11177,6 +11572,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116782</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11307,6 +11707,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116783</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11437,6 +11842,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116784</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11567,6 +11977,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850331</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11697,6 +12112,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850332</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11827,6 +12247,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850333</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11957,6 +12382,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850334</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12087,6 +12517,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850335</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12217,6 +12652,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850336</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12347,6 +12787,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850341</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12477,6 +12922,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850344</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12607,6 +13057,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850345</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12737,6 +13192,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850348</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12867,6 +13327,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850349</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12997,6 +13462,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850350</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13127,6 +13597,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850354</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13257,6 +13732,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850355</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13387,6 +13867,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850356</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13517,6 +14002,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850357</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13647,6 +14137,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850358</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13777,6 +14272,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850359</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13907,6 +14407,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850360</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14037,6 +14542,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850362</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14167,6 +14677,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850363</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14297,6 +14812,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850365</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14427,6 +14947,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850366</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14557,6 +15082,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850368</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14687,6 +15217,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850369</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14817,6 +15352,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850371</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14947,6 +15487,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850373</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15077,6 +15622,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850374</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -15207,6 +15757,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850375</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15337,6 +15892,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850376</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15467,6 +16027,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850377</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15597,6 +16162,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850378</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15727,6 +16297,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850379</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15857,6 +16432,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850380</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15987,6 +16567,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850381</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16117,6 +16702,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850382</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16247,6 +16837,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850383</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -16377,6 +16972,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850384</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16511,6 +17111,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040783</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16645,6 +17250,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040873</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16779,6 +17389,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040875</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16913,6 +17528,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040876</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17047,6 +17667,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040878</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17181,6 +17806,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041012</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17315,6 +17945,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041185</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17440,6 +18075,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675620</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17565,6 +18205,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675622</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17690,6 +18335,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675627</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17815,6 +18465,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675629</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -17954,6 +18609,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062640</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18093,6 +18753,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062641</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -18232,6 +18897,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062644</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18371,6 +19041,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635473</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -18510,6 +19185,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635474</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18649,6 +19329,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635475</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18788,6 +19473,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635476</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18927,6 +19617,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635477</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19066,6 +19761,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635478</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -19205,6 +19905,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635479</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -19312,8 +20017,156 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78165259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>